--- a/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
+++ b/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-india\InputData\trans\RTMF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\trans\RTMF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923D0318-1CE6-4154-B16D-6EA15463A7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879C9A3C-65AE-46B7-AAAF-3BEC51FB4A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="260" windowWidth="19190" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12870" yWindow="1470" windowWidth="22500" windowHeight="21135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="IndiaCalcs- Web Guidance" sheetId="4" r:id="rId2"/>
-    <sheet name="RTMF-passengers" sheetId="2" r:id="rId3"/>
-    <sheet name="RTMF-freight" sheetId="3" r:id="rId4"/>
+    <sheet name="RTMF-passengers" sheetId="2" r:id="rId2"/>
+    <sheet name="RTMF-freight" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,6 +28,7 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>RTMF Recipient Transportation Mode Fractions</t>
   </si>
@@ -143,74 +143,11 @@
   <si>
     <t>the following mode shifts:</t>
   </si>
-  <si>
-    <t>BAU</t>
-  </si>
-  <si>
-    <t>Cars</t>
-  </si>
-  <si>
-    <t>2ws</t>
-  </si>
-  <si>
-    <t>3ws</t>
-  </si>
-  <si>
-    <t>bus</t>
-  </si>
-  <si>
-    <t>nmt</t>
-  </si>
-  <si>
-    <t>change</t>
-  </si>
-  <si>
-    <t>shift-to</t>
-  </si>
-  <si>
-    <t>shift-from</t>
-  </si>
-  <si>
-    <t>ratios of target modes</t>
-  </si>
-  <si>
-    <t>Sustainable Scenario</t>
-  </si>
-  <si>
-    <t>Mode shares in 2050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: </t>
-  </si>
-  <si>
-    <t>https://orbit.dtu.dk/files/120569095/Transport_Scenarios_for_India.pdf</t>
-  </si>
-  <si>
-    <t>Passenger Private Transport</t>
-  </si>
-  <si>
-    <t>Freight HDVs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"In the High Rail Scenario, a modal shift to </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rail occurs.. in freight transport (mainly) away </t>
-  </si>
-  <si>
-    <t>from heavy trucks"</t>
-  </si>
-  <si>
-    <t>https://www.iea.org/reports/the-future-of-rail</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -245,7 +182,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,26 +195,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -285,39 +204,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -325,21 +216,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,99 +231,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>172463</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>182544</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE3A85D-E566-4907-8CCC-8D20F9F02963}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7858125" y="0"/>
-          <a:ext cx="4954013" cy="2659044"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>548377</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>10094</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC61108-1913-413A-A894-2E04D3DC4B1B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3057525" y="3400425"/>
-          <a:ext cx="5863327" cy="3658169"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -874,237 +657,222 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L39"/>
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="E1" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E2" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="9">
-        <v>25</v>
-      </c>
-      <c r="F3" s="9">
-        <v>19</v>
-      </c>
-      <c r="G3" s="13">
-        <f t="shared" ref="G3:G8" si="0">F3-E3</f>
-        <v>-6</v>
-      </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13">
-        <f>SUM(G3:G5)</f>
-        <v>-13</v>
-      </c>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="9">
-        <f>52-E3</f>
-        <v>27</v>
-      </c>
-      <c r="F4" s="9">
-        <f>40-F3</f>
-        <v>21</v>
-      </c>
-      <c r="G4" s="13">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6">
+        <f>1-SUM(B2:G2)</f>
+        <v>0.33999999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6">
         <f t="shared" si="0"/>
-        <v>-6</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="9">
-        <f>58-52</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="9">
-        <f>45-40</f>
-        <v>5</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6">
         <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="9">
-        <f>82-58</f>
-        <v>24</v>
-      </c>
-      <c r="F6" s="9">
-        <f>77-45</f>
-        <v>32</v>
-      </c>
-      <c r="G6" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6">
         <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="14">
-        <f>SUM(G6:G8)</f>
-        <v>13</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10">
-        <f>G6/$H$6</f>
-        <v>0.61538461538461542</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="9">
-        <f>91-82</f>
-        <v>9</v>
-      </c>
-      <c r="F7" s="9">
-        <f>88-77</f>
-        <v>11</v>
-      </c>
-      <c r="G7" s="14">
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10">
-        <f>G7/$H$6</f>
-        <v>0.15384615384615385</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="9">
-        <f>100-91</f>
-        <v>9</v>
-      </c>
-      <c r="F8" s="9">
-        <f>100-88</f>
-        <v>12</v>
-      </c>
-      <c r="G8" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10">
-        <f>G8/$H$6</f>
-        <v>0.23076923076923078</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E9" s="9">
-        <f>SUM(E3:E8)</f>
-        <v>100</v>
-      </c>
-      <c r="F9" s="9">
-        <f>SUM(F3:F8)</f>
-        <v>100</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K16" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="8"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F39" t="s">
-        <v>43</v>
-      </c>
-      <c r="G39" t="s">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E1:F1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1154,16 +922,14 @@
       <c r="B2" s="4">
         <v>0</v>
       </c>
-      <c r="C2" s="15">
-        <f>'IndiaCalcs- Web Guidance'!J6</f>
-        <v>0.61538461538461542</v>
+      <c r="C2" s="4">
+        <v>0</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
-        <f>'IndiaCalcs- Web Guidance'!J7</f>
-        <v>0.15384615384615385</v>
+      <c r="E2" s="4">
+        <v>0</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -1172,9 +938,9 @@
         <v>0</v>
       </c>
       <c r="H2" s="4"/>
-      <c r="I2" s="16">
+      <c r="I2" s="6">
         <f>1-SUM(B2:G2)</f>
-        <v>0.23076923076923073</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1219,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
@@ -1230,7 +996,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="6">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1265,34 +1031,28 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15">
-        <f>B2</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="15">
-        <f>C2</f>
-        <v>0.61538461538461542</v>
-      </c>
-      <c r="D6" s="15">
-        <f t="shared" ref="D6:G6" si="1">D2</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <f t="shared" si="1"/>
-        <v>0.15384615384615385</v>
-      </c>
-      <c r="F6" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" si="1"/>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="16">
-        <f>1-SUM(B6:G6)</f>
-        <v>0.23076923076923073</v>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1302,16 +1062,14 @@
       <c r="B7" s="4">
         <v>0</v>
       </c>
-      <c r="C7" s="15">
-        <f>C2</f>
-        <v>0.61538461538461542</v>
+      <c r="C7" s="4">
+        <v>0</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
       </c>
-      <c r="E7" s="15">
-        <f>E2</f>
-        <v>0.15384615384615385</v>
+      <c r="E7" s="4">
+        <v>0</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -1320,9 +1078,9 @@
         <v>0</v>
       </c>
       <c r="H7" s="4"/>
-      <c r="I7" s="16">
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
-        <v>0.23076923076923073</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1337,225 +1095,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6">
-        <f>1-SUM(B2:G2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="6">
-        <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.33</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0.33</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="6">
-        <f t="shared" si="0"/>
-        <v>0.33999999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
+++ b/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\trans\RTMF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\RTMF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879C9A3C-65AE-46B7-AAAF-3BEC51FB4A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2643F14-5F7F-4432-8B4A-9A19F1481256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12870" yWindow="1470" windowWidth="22500" windowHeight="21135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>RTMF Recipient Transportation Mode Fractions</t>
   </si>
@@ -138,10 +138,16 @@
     <t>goes to a mix of passenger rail and non-motorized/eliminated</t>
   </si>
   <si>
-    <t>goes to a mix of freight rail and freight ships</t>
-  </si>
-  <si>
     <t>the following mode shifts:</t>
+  </si>
+  <si>
+    <t>freight rail</t>
+  </si>
+  <si>
+    <t>goes to reduced VMT, representing freight logistics</t>
+  </si>
+  <si>
+    <t>goes to reduced VMT, representing lower demand for coal transport</t>
   </si>
 </sst>
 </file>
@@ -208,12 +214,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -234,9 +238,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -274,7 +278,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -380,7 +384,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -522,7 +526,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -530,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -600,30 +604,26 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-    </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>30</v>
+      <c r="A25" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
@@ -632,7 +632,6 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
@@ -641,12 +640,19 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +666,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -669,7 +675,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -690,7 +696,7 @@
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -698,26 +704,25 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.33</v>
       </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>0.33</v>
       </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
         <f>1-SUM(B2:G2)</f>
         <v>0.33999999999999997</v>
       </c>
@@ -726,26 +731,25 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="6">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
         <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
         <v>1</v>
       </c>
@@ -754,26 +758,25 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>0.25</v>
       </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -782,26 +785,25 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="6">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -810,26 +812,25 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="6">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -838,38 +839,28 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="6">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -881,7 +872,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -890,7 +881,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -911,7 +902,7 @@
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -919,26 +910,25 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
         <f>1-SUM(B2:G2)</f>
         <v>1</v>
       </c>
@@ -947,26 +937,25 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="6">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
         <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
         <v>1</v>
       </c>
@@ -975,26 +964,25 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1003,26 +991,25 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="6">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1031,26 +1018,25 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="6">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1059,38 +1045,28 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="6">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
